--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>86.0136570095957</v>
+        <v>13.9772192640593</v>
       </c>
       <c r="D2" t="n">
-        <v>84.50329860911522</v>
+        <v>13.73178602398122</v>
       </c>
       <c r="E2" t="n">
-        <v>23.18738982697985</v>
+        <v>3.767950846884226</v>
       </c>
       <c r="F2" t="n">
-        <v>22.28368418124945</v>
+        <v>3.621098679453036</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.48366988969128</v>
+        <v>6.091096357074833</v>
       </c>
       <c r="D3" t="n">
-        <v>34.87931479609151</v>
+        <v>5.667888654364871</v>
       </c>
       <c r="E3" t="n">
-        <v>23.18738982697985</v>
+        <v>3.767950846884226</v>
       </c>
       <c r="F3" t="n">
-        <v>22.28368418124945</v>
+        <v>3.621098679453036</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.64410091260592</v>
+        <v>10.50466639829846</v>
       </c>
       <c r="D4" t="n">
-        <v>63.55181577746434</v>
+        <v>10.32717006383796</v>
       </c>
       <c r="E4" t="n">
-        <v>23.18738982697985</v>
+        <v>3.767950846884226</v>
       </c>
       <c r="F4" t="n">
-        <v>22.28368418124945</v>
+        <v>3.621098679453036</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.79814278575462</v>
+        <v>4.354698202685126</v>
       </c>
       <c r="D5" t="n">
-        <v>29.46000540137771</v>
+        <v>4.787250877723878</v>
       </c>
       <c r="E5" t="n">
-        <v>23.18738982697985</v>
+        <v>3.767950846884226</v>
       </c>
       <c r="F5" t="n">
-        <v>22.28368418124945</v>
+        <v>3.621098679453036</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
